--- a/output/Bao_Cao_Hop_Nhat_Q2_2026.xlsx
+++ b/output/Bao_Cao_Hop_Nhat_Q2_2026.xlsx
@@ -12314,8 +12314,9 @@
         </is>
       </c>
       <c r="C78" s="418" t="n"/>
-      <c r="D78" s="540" t="n">
-        <v>50000000000</v>
+      <c r="D78" s="540">
+        <f>'so lieu'!G36</f>
+        <v/>
       </c>
       <c r="E78" s="540" t="n">
         <v>50000000000</v>
@@ -12472,8 +12473,9 @@
         </is>
       </c>
       <c r="C84" s="418" t="n"/>
-      <c r="D84" s="540" t="n">
-        <v>9129514079</v>
+      <c r="D84" s="540">
+        <f>'so lieu'!G37+'so lieu'!G38</f>
+        <v/>
       </c>
       <c r="E84" s="540" t="n">
         <v>9129514079</v>
@@ -15951,8 +15953,9 @@
         </is>
       </c>
       <c r="C50" s="135" t="n"/>
-      <c r="D50" s="591" t="n">
-        <v>58000000000</v>
+      <c r="D50" s="591">
+        <f>'so lieu'!B3</f>
+        <v/>
       </c>
       <c r="E50" s="591" t="n">
         <v>72000000000</v>
@@ -17630,8 +17633,9 @@
         </is>
       </c>
       <c r="C112" s="115" t="n"/>
-      <c r="D112" s="585" t="n">
-        <v>512482745684</v>
+      <c r="D112" s="585">
+        <f>'so lieu'!B1+'so lieu'!B2+'so lieu'!B4</f>
+        <v/>
       </c>
       <c r="E112" s="585" t="n">
         <v>194465890088</v>
@@ -17669,7 +17673,10 @@
         </is>
       </c>
       <c r="C113" s="115" t="n"/>
-      <c r="D113" s="585" t="n"/>
+      <c r="D113" s="585">
+        <f>D114-D111-D112</f>
+        <v/>
+      </c>
       <c r="E113" s="585" t="n"/>
       <c r="F113" s="451" t="inlineStr">
         <is>
@@ -20670,8 +20677,9 @@
           <t>1. Thuế GTGT</t>
         </is>
       </c>
-      <c r="B199" s="656" t="n">
-        <v>327740170</v>
+      <c r="B199" s="656">
+        <f>Thue!D12</f>
+        <v/>
       </c>
       <c r="C199" s="656">
         <f>Thue!E12</f>
@@ -20716,8 +20724,9 @@
           <t>3. Thuế TNDN</t>
         </is>
       </c>
-      <c r="B202" s="656" t="n">
-        <v>1699375943</v>
+      <c r="B202" s="656">
+        <f>Thue!D16</f>
+        <v/>
       </c>
       <c r="C202" s="656">
         <f>Thue!E16</f>
@@ -21567,26 +21576,26 @@
       </c>
       <c r="C11" s="661" t="n"/>
       <c r="D11" s="666" t="n">
-        <v>2104207557</v>
+        <v>1122238566</v>
       </c>
       <c r="E11" s="666" t="n">
-        <v>2247355787</v>
+        <v>2575387900</v>
       </c>
       <c r="F11" s="666" t="n">
-        <v>3229324778</v>
+        <v>1894092838</v>
       </c>
       <c r="G11" s="666" t="n">
-        <v>2247355787</v>
+        <v>2575387900</v>
       </c>
       <c r="H11" s="662" t="n"/>
       <c r="I11" s="662" t="n"/>
       <c r="J11" s="662" t="n"/>
       <c r="K11" s="661" t="n"/>
       <c r="L11" s="666" t="n">
-        <v>3229324778</v>
+        <v>1894092838</v>
       </c>
       <c r="M11" s="666" t="n">
-        <v>1122238566</v>
+        <v>1803533628</v>
       </c>
       <c r="N11" s="388" t="n"/>
     </row>
@@ -21603,26 +21612,26 @@
       </c>
       <c r="C12" s="661" t="n"/>
       <c r="D12" s="667" t="n">
-        <v>327740170</v>
+        <v>333201502</v>
       </c>
       <c r="E12" s="667" t="n">
-        <v>929981117</v>
+        <v>1335096028</v>
       </c>
       <c r="F12" s="667" t="n">
-        <v>924519785</v>
+        <v>1311751576</v>
       </c>
       <c r="G12" s="667" t="n">
-        <v>929981117</v>
+        <v>1335096028</v>
       </c>
       <c r="H12" s="662" t="n"/>
       <c r="I12" s="662" t="n"/>
       <c r="J12" s="662" t="n"/>
       <c r="K12" s="661" t="n"/>
       <c r="L12" s="667" t="n">
-        <v>924519785</v>
+        <v>1311751576</v>
       </c>
       <c r="M12" s="667" t="n">
-        <v>333201502</v>
+        <v>356545954</v>
       </c>
       <c r="N12" s="388" t="n"/>
     </row>
@@ -21747,26 +21756,26 @@
       </c>
       <c r="C16" s="661" t="n"/>
       <c r="D16" s="667" t="n">
-        <v>1699375943</v>
+        <v>778687531</v>
       </c>
       <c r="E16" s="667" t="n">
-        <v>778687531</v>
+        <v>1086773307</v>
       </c>
       <c r="F16" s="667" t="n">
-        <v>1699375943</v>
+        <v>500000000</v>
       </c>
       <c r="G16" s="667" t="n">
-        <v>778687531</v>
+        <v>1086773307</v>
       </c>
       <c r="H16" s="662" t="n"/>
       <c r="I16" s="662" t="n"/>
       <c r="J16" s="662" t="n"/>
       <c r="K16" s="661" t="n"/>
       <c r="L16" s="667" t="n">
-        <v>1699375943</v>
+        <v>500000000</v>
       </c>
       <c r="M16" s="667" t="n">
-        <v>778687531</v>
+        <v>1365460838</v>
       </c>
       <c r="N16" s="388" t="n"/>
     </row>
@@ -21783,26 +21792,26 @@
       </c>
       <c r="C17" s="661" t="n"/>
       <c r="D17" s="667" t="n">
-        <v>77091444</v>
+        <v>10349533</v>
       </c>
       <c r="E17" s="667" t="n">
-        <v>536486035</v>
+        <v>151527729</v>
       </c>
       <c r="F17" s="667" t="n">
-        <v>603227946</v>
+        <v>80350426</v>
       </c>
       <c r="G17" s="667" t="n">
-        <v>536486035</v>
+        <v>151527729</v>
       </c>
       <c r="H17" s="662" t="n"/>
       <c r="I17" s="662" t="n"/>
       <c r="J17" s="662" t="n"/>
       <c r="K17" s="661" t="n"/>
       <c r="L17" s="667" t="n">
-        <v>603227946</v>
+        <v>80350426</v>
       </c>
       <c r="M17" s="667" t="n">
-        <v>10349533</v>
+        <v>81526836</v>
       </c>
       <c r="N17" s="388" t="n"/>
     </row>
@@ -21930,20 +21939,20 @@
         <v>0</v>
       </c>
       <c r="E21" s="667" t="n">
-        <v>2201104</v>
+        <v>1990836</v>
       </c>
       <c r="F21" s="667" t="n">
-        <v>2201104</v>
+        <v>1990836</v>
       </c>
       <c r="G21" s="667" t="n">
-        <v>2201104</v>
+        <v>1990836</v>
       </c>
       <c r="H21" s="662" t="n"/>
       <c r="I21" s="662" t="n"/>
       <c r="J21" s="662" t="n"/>
       <c r="K21" s="661" t="n"/>
       <c r="L21" s="667" t="n">
-        <v>2201104</v>
+        <v>1990836</v>
       </c>
       <c r="M21" s="667" t="n">
         <v>0</v>
@@ -22107,26 +22116,26 @@
       </c>
       <c r="C26" s="661" t="n"/>
       <c r="D26" s="666" t="n">
-        <v>2104207557</v>
+        <v>1122238566</v>
       </c>
       <c r="E26" s="666" t="n">
-        <v>2247355787</v>
+        <v>2575387900</v>
       </c>
       <c r="F26" s="666" t="n">
-        <v>3229324778</v>
+        <v>1894092838</v>
       </c>
       <c r="G26" s="666" t="n">
-        <v>2247355787</v>
+        <v>2575387900</v>
       </c>
       <c r="H26" s="662" t="n"/>
       <c r="I26" s="662" t="n"/>
       <c r="J26" s="662" t="n"/>
       <c r="K26" s="661" t="n"/>
       <c r="L26" s="666" t="n">
-        <v>3229324778</v>
+        <v>1894092838</v>
       </c>
       <c r="M26" s="666" t="n">
-        <v>1122238566</v>
+        <v>1803533628</v>
       </c>
       <c r="N26" s="388" t="n"/>
     </row>
@@ -30502,30 +30511,26 @@
       </c>
     </row>
     <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Chênh lệch (Nợ - Có)</t>
+        </is>
+      </c>
       <c r="B86" s="668">
-        <f>B85-[4]Sheet1!C65</f>
-        <v/>
-      </c>
-      <c r="C86" s="668">
-        <f>C85-[4]Sheet1!D65</f>
-        <v/>
-      </c>
+        <f>B85-C85</f>
+        <v/>
+      </c>
+      <c r="C86" s="668" t="n"/>
       <c r="D86" s="668">
-        <f>D85-[4]Sheet1!E65</f>
-        <v/>
-      </c>
-      <c r="E86" s="668">
-        <f>E85-[4]Sheet1!F65</f>
-        <v/>
-      </c>
+        <f>D85-E85</f>
+        <v/>
+      </c>
+      <c r="E86" s="668" t="n"/>
       <c r="F86" s="668">
-        <f>F85-[4]Sheet1!G65</f>
-        <v/>
-      </c>
-      <c r="G86" s="668">
-        <f>G85-[4]Sheet1!H65</f>
-        <v/>
-      </c>
+        <f>F85-G85</f>
+        <v/>
+      </c>
+      <c r="G86" s="668" t="n"/>
       <c r="J86" s="674" t="n"/>
       <c r="K86" s="274" t="n">
         <v>185339361569</v>
